--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_090_Solomon_Isl.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_090_Solomon_Isl.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R96635933c92648c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R707176e1972c4610"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R0376920418244691"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Re2ea3e5719f24635"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R91d179467f1c481e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R6cdb25c94ca54d05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R22886f6df869405d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rf268003e05d24027"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R7715031404bd4b14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R47b70cded47e4c2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Re50b48138b7e48b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R28e9d9021a964741"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ090CommercialTable" displayName="EEZ090CommercialTable" ref="A1:O9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O9"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ090CommercialTable" displayName="EEZ090CommercialTable" ref="A1:E9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E9"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ090FunctionalTable" displayName="EEZ090FunctionalTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ090FunctionalTable" displayName="EEZ090FunctionalTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ090ValidationTable" displayName="EEZ090ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ090ValidationTable" displayName="EEZ090ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -4178,7 +4132,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42aec789079a4e48"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73a327e2ba5940d6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4188,20 +4142,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4209,498 +4153,174 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>35.319549658</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.3042105263141806</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>201.4700648901084</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>35.319549658</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>204.7083885547631</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$53,A2,'Species'!$U$2:$U$53))</x:f>
-        <x:v>7230.208094969114</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.3042105263141806</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>201.4700648901084</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>7115.831961486666</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>114.3761334824485</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0160734730810805</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.016073473081080543</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>4513.105996222</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.979937445256556</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>95.48550410685282</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>4513.105996222</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>142.09632052976139</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$53,A3,'Species'!$U$2:$U$53))</x:f>
-        <x:v>641295.7562239494</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.979937445256556</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>95.48550410685282</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>430936.2011369178</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>210359.55508703156</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.4881454714921845</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.4881454714921844</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1.858923666</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.335</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>216.271852372702</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1.858923666</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>248.7138851382946</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$53,A4,'Species'!$U$2:$U$53))</x:f>
-        <x:v>462.34012714638146</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.335</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>216.271852372702</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>402.03286466527396</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>60.3072624811075</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1500058024642297</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.15000580246422976</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2414.697152011</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.118897218611542</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>13.149136041081583</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2414.697152011</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>13.150963852128825</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$53,A5,'Species'!$U$2:$U$53))</x:f>
-        <x:v>31755.594959935086</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.118897218611542</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>13.149136041081583</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>31751.181349804894</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>4.413610130191955</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.00013900617056</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.00013900617055998378</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>6452.9560205107</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.271676305452227</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>186.92883763882378</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>6452.9560205107</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>193.22897958641104</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$53,A6,'Species'!$U$2:$U$53))</x:f>
-        <x:v>1246898.1071592702</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.271676305452227</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>186.92883763882378</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1206243.568248515</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>40654.53891075519</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.033703424400253</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.03370342440025295</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>24026.858785578697</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.094776318025945</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1243.8737935689765</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>24026.858785578697</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1343.6270277016977</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$53,A7,'Species'!$U$2:$U$53))</x:f>
-        <x:v>32283136.855075527</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.094776318025945</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1243.8737935689765</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>29886379.985163864</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>2396756.8699116632</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.080195623260544</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.08019562326054398</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>12566.0513253922</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.3530633318829</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2254.5679651755136</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>12566.0513253922</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2300.409323972101</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$53,A8,'Species'!$U$2:$U$53))</x:f>
-        <x:v>28907061.634444192</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.3530633318829</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2254.5679651755136</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>28331016.76698056</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>576044.8674636334</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0203326577440386</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.020332657744038557</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>92750.13375085029</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.413785142146215</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2592.8962650954877</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>92750.13375085029</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2605.0572437045134</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$53,A9,'Species'!$U$2:$U$53))</x:f>
-        <x:v>241619407.78221503</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.413785142146215</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2592.8962650954877</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>240491475.38968664</x:v>
       </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1127932.392528385</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0046901138208775</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.004690113820877477</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G9">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O9">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66e1150fa14c4b9c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dd6ba17b75e43b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4710,20 +4330,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4731,660 +4341,231 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>24.836630550000002</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.21</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1621.8100973589299</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>24.836630550000002</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1621.8100973589299</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$53,A2,'Species'!$U$2:$U$53))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>40280.298210363275</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.21</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1621.8100973589299</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>40280.298210363275</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>93578.23141300821</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.413252832444813</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2589.720129138349</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>93578.23141300821</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2602.058348543165</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$53,A3,'Species'!$U$2:$U$53))</x:f>
-        <x:v>243496018.29012224</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.413252832444813</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2589.720129138349</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>242341429.53943393</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1154588.7506883144</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0047643060985594</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.004764306098559343</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>12566.0513253922</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.3530633318829</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2254.5679651755136</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>12566.0513253922</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2300.409323972101</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$53,A4,'Species'!$U$2:$U$53))</x:f>
-        <x:v>28907061.634444192</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.3530633318829</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2254.5679651755136</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>28331016.76698056</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>576044.8674636334</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0203326577440386</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.020332657744038557</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>4498.105996222</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.977302794509974</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>94.90799408237768</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>4498.105996222</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>140.60653571188118</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$53,A5,'Species'!$U$2:$U$53))</x:f>
-        <x:v>632463.1013936155</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.977302794509974</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>94.90799408237768</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>426906.21727134514</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>205556.88412227033</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.481503608535213</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.48150360853521296</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>5291.7050897242</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.28</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>190.54607179632464</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>5291.7050897242</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>190.54607179632464</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$53,A6,'Species'!$U$2:$U$53))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1008313.6179515639</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.28</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>190.54607179632464</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>1008313.6179515639</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>3208.8476009783</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.915841079034434</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>823.8365941095684</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>3208.8476009783</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1148.4020526691827</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$53,A7,'Species'!$U$2:$U$53))</x:f>
-        <x:v>3685047.171666062</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.915841079034434</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>823.8365941095684</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2643566.078606622</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>1041481.0930594401</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.3939682467133134</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.39396824671331343</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>21026.327822679</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.074162244038314</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1186.2118112456958</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>21026.327822679</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1280.2417803771234</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$53,A8,'Species'!$U$2:$U$53))</x:f>
-        <x:v>26918783.366499607</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.074162244038314</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1186.2118112456958</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>24941678.41038582</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1977104.9561137855</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0792691222933302</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.07926912229333014</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>2514.697152011</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>2.114169125667369</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>13.006759967840857</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>2514.697152011</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>13.02566193059887</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$53,A9,'Species'!$U$2:$U$53))</x:f>
-        <x:v>32755.594959935086</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>2.114169125667369</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>13.006759967840857</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>32708.06224802009</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>47.53271191499516</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.001453241453271</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0014532414532711258</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>15</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.77</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>588.843655355589</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>588.843655355589</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$53,A10,'Species'!$U$2:$U$53))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>8832.654830333835</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.77</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>588.843655355589</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>8832.654830333835</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>36.249011491</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.3110256410233214</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>204.65654636886148</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>36.249011491</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>208.98599985025032</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$53,A11,'Species'!$U$2:$U$53))</x:f>
-        <x:v>7575.535910029847</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.3110256410233214</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>204.65654636886148</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>7418.597501033234</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>156.93840899661336</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0211547275579724</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.021154727557972458</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>0.929461833</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.1</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>125.89254117941675</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>0.929461833</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>125.89254117941675</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$53,A12,'Species'!$U$2:$U$53))</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>117.01231208564867</x:v>
       </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.1</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>125.89254117941675</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
-        <x:v>117.01231208564867</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f1ecc94bd3941a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R488b0649970f4d0c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5559,7 +4740,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -5658,7 +4839,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>304737248.27830005</x:v>
+        <x:v>300385320.9573925</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5672,7 +4853,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>304737248.27830005</x:v>
+        <x:v>299782267.2557317</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5686,7 +4867,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-4351927.320907533</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5700,7 +4881,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-4954981.022568345</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -5711,9 +4892,9 @@
         <x:v>EEZ_090</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -5725,47 +4906,19 @@
         <x:v>EEZ_090</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_090</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_090</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7ee3dd17d5943a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91f0f7e8c1674609"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5812,7 +4965,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
